--- a/artfynd/A 56879-2025 artfynd.xlsx
+++ b/artfynd/A 56879-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -789,6 +789,103 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>130243790</v>
+      </c>
+      <c r="B3" t="n">
+        <v>79095</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Hassikmossen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>474454</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6654230</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 56879-2025 artfynd.xlsx
+++ b/artfynd/A 56879-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130218006</v>
       </c>
       <c r="B2" t="n">
-        <v>56931</v>
+        <v>57016</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>130243790</v>
       </c>
       <c r="B3" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 56879-2025 artfynd.xlsx
+++ b/artfynd/A 56879-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>130243790</v>
       </c>
       <c r="B3" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 56879-2025 artfynd.xlsx
+++ b/artfynd/A 56879-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130218006</v>
       </c>
       <c r="B2" t="n">
-        <v>57016</v>
+        <v>57042</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>130243790</v>
       </c>
       <c r="B3" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 56879-2025 artfynd.xlsx
+++ b/artfynd/A 56879-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130218006</v>
       </c>
       <c r="B2" t="n">
-        <v>57042</v>
+        <v>57044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>130243790</v>
       </c>
       <c r="B3" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 56879-2025 artfynd.xlsx
+++ b/artfynd/A 56879-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,55 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130218006</v>
+        <v>130243790</v>
       </c>
       <c r="B2" t="n">
-        <v>57044</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hassikmossen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>474471</v>
+        <v>474454</v>
       </c>
       <c r="R2" t="n">
-        <v>6654255</v>
+        <v>6654230</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>15:03</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>15:03</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,14 +772,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130243790</v>
+        <v>130243804</v>
       </c>
       <c r="B3" t="n">
-        <v>79211</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -827,13 +807,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>474454</v>
+        <v>474455</v>
       </c>
       <c r="R3" t="n">
-        <v>6654230</v>
+        <v>6654252</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -886,6 +866,123 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>130218006</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Hassikmossen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>474471</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6654255</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-12-19</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-12-19</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
